--- a/reports/latest/Automation_Test_Report.xlsx
+++ b/reports/latest/Automation_Test_Report.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
     </row>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
     </row>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
     </row>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
     </row>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
     </row>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
     </row>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
     </row>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
     </row>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
     </row>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
     </row>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
     </row>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
     </row>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
     </row>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
     </row>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
     </row>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
     </row>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
     </row>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
     </row>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
     </row>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
     </row>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
     </row>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
     </row>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
     </row>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
     </row>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
     </row>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
     </row>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
     </row>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
     </row>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
     </row>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
     </row>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
     </row>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
     </row>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
     </row>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
     </row>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
     </row>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
     </row>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
     </row>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
     </row>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
     </row>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
     </row>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
     </row>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
     </row>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
     </row>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
     </row>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
     </row>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
     </row>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
     </row>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
     </row>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
     </row>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
     </row>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
     </row>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
     </row>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
     </row>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
     </row>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
     </row>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
     </row>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
     </row>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
     </row>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
     </row>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
     </row>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
     </row>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
     </row>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
     </row>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
     </row>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
     </row>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
     </row>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
     </row>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
     </row>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
     </row>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
     </row>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
     </row>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
     </row>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
     </row>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
     </row>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
     </row>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
     </row>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
     </row>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
     </row>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
     </row>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
     </row>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
     </row>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
     </row>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
     </row>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
     </row>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
     </row>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
     </row>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
     </row>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
     </row>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
     </row>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
     </row>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
     </row>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
     </row>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
     </row>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
     </row>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
     </row>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
     </row>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
     </row>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
     </row>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
     </row>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
     </row>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="G155" s="2" t="inlineStr"/>
     </row>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
     </row>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
     </row>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
     </row>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
     </row>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
     </row>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
     </row>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
     </row>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
     </row>
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
     </row>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
     </row>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
     </row>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
     </row>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
     </row>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
     </row>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
     </row>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
     </row>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
     </row>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
     </row>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
     </row>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G177" s="2" t="inlineStr"/>
     </row>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
     </row>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
     </row>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
     </row>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
     </row>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
     </row>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
     </row>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
     </row>
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
     </row>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G187" s="2" t="inlineStr"/>
     </row>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
     </row>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
     </row>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
     </row>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="G193" s="2" t="inlineStr"/>
     </row>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G194" s="2" t="inlineStr"/>
     </row>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="G195" s="2" t="inlineStr"/>
     </row>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="G197" s="2" t="inlineStr"/>
     </row>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="G198" s="2" t="inlineStr"/>
     </row>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G199" s="2" t="inlineStr"/>
     </row>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="G200" s="2" t="inlineStr"/>
     </row>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="G201" s="2" t="inlineStr"/>
     </row>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
     </row>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G203" s="2" t="inlineStr"/>
     </row>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G204" s="2" t="inlineStr"/>
     </row>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="G205" s="2" t="inlineStr"/>
     </row>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G206" s="2" t="inlineStr"/>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="G207" s="2" t="inlineStr"/>
     </row>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G208" s="2" t="inlineStr"/>
     </row>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="G210" s="2" t="inlineStr"/>
     </row>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G212" s="2" t="inlineStr"/>
     </row>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G213" s="2" t="inlineStr"/>
     </row>
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="G214" s="2" t="inlineStr"/>
     </row>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G215" s="2" t="inlineStr"/>
     </row>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="G217" s="2" t="inlineStr"/>
     </row>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G218" s="2" t="inlineStr"/>
     </row>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
     </row>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
     </row>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G221" s="2" t="inlineStr"/>
     </row>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G222" s="2" t="inlineStr"/>
     </row>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G223" s="2" t="inlineStr"/>
     </row>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="G224" s="2" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G225" s="2" t="inlineStr"/>
     </row>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="G226" s="2" t="inlineStr"/>
     </row>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G227" s="2" t="inlineStr"/>
     </row>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G228" s="2" t="inlineStr"/>
     </row>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="G229" s="2" t="inlineStr"/>
     </row>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G230" s="2" t="inlineStr"/>
     </row>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G231" s="2" t="inlineStr"/>
     </row>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G232" s="2" t="inlineStr"/>
     </row>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G233" s="2" t="inlineStr"/>
     </row>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="G234" s="2" t="inlineStr"/>
     </row>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G235" s="2" t="inlineStr"/>
     </row>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G236" s="2" t="inlineStr"/>
     </row>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G237" s="2" t="inlineStr"/>
     </row>
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G238" s="2" t="inlineStr"/>
     </row>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G239" s="2" t="inlineStr"/>
     </row>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="G241" s="2" t="inlineStr"/>
     </row>
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="G242" s="2" t="inlineStr"/>
     </row>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G244" s="2" t="inlineStr"/>
     </row>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G245" s="2" t="inlineStr"/>
     </row>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G246" s="2" t="inlineStr"/>
     </row>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="G247" s="2" t="inlineStr"/>
     </row>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G248" s="2" t="inlineStr"/>
     </row>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G249" s="2" t="inlineStr"/>
     </row>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G250" s="2" t="inlineStr"/>
     </row>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G251" s="2" t="inlineStr"/>
     </row>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="G253" s="2" t="inlineStr"/>
     </row>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="G254" s="2" t="inlineStr"/>
     </row>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="G256" s="2" t="inlineStr"/>
     </row>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G257" s="2" t="inlineStr"/>
     </row>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G258" s="2" t="inlineStr"/>
     </row>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G259" s="2" t="inlineStr"/>
     </row>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G260" s="2" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G261" s="2" t="inlineStr"/>
     </row>
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G262" s="2" t="inlineStr"/>
     </row>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="G263" s="2" t="inlineStr"/>
     </row>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G264" s="2" t="inlineStr"/>
     </row>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G265" s="2" t="inlineStr"/>
     </row>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="G266" s="2" t="inlineStr"/>
     </row>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G268" s="2" t="inlineStr"/>
     </row>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G269" s="2" t="inlineStr"/>
     </row>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G270" s="2" t="inlineStr"/>
     </row>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="G271" s="2" t="inlineStr"/>
     </row>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G272" s="2" t="inlineStr"/>
     </row>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="G273" s="2" t="inlineStr"/>
     </row>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="G274" s="2" t="inlineStr"/>
     </row>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G275" s="2" t="inlineStr"/>
     </row>
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G276" s="2" t="inlineStr"/>
     </row>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G277" s="2" t="inlineStr"/>
     </row>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="G279" s="2" t="inlineStr"/>
     </row>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G280" s="2" t="inlineStr"/>
     </row>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G281" s="2" t="inlineStr"/>
     </row>
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G282" s="2" t="inlineStr"/>
     </row>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G284" s="2" t="inlineStr"/>
     </row>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="G285" s="2" t="inlineStr"/>
     </row>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="G286" s="2" t="inlineStr"/>
     </row>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G287" s="2" t="inlineStr"/>
     </row>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="G288" s="2" t="inlineStr"/>
     </row>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G289" s="2" t="inlineStr"/>
     </row>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G290" s="2" t="inlineStr"/>
     </row>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="G291" s="2" t="inlineStr"/>
     </row>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G292" s="2" t="inlineStr"/>
     </row>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G293" s="2" t="inlineStr"/>
     </row>
@@ -9584,7 +9584,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G294" s="2" t="inlineStr"/>
     </row>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="G295" s="2" t="inlineStr"/>
     </row>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G296" s="2" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G297" s="2" t="inlineStr"/>
     </row>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="G298" s="2" t="inlineStr"/>
     </row>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G299" s="2" t="inlineStr"/>
     </row>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="G300" s="2" t="inlineStr"/>
     </row>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G301" s="2" t="inlineStr"/>
     </row>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="G302" s="2" t="inlineStr"/>
     </row>
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G303" s="2" t="inlineStr"/>
     </row>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G304" s="2" t="inlineStr"/>
     </row>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="G305" s="2" t="inlineStr"/>
     </row>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G306" s="2" t="inlineStr"/>
     </row>
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="G307" s="2" t="inlineStr"/>
     </row>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="G308" s="2" t="inlineStr"/>
     </row>
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G309" s="2" t="inlineStr"/>
     </row>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="G310" s="2" t="inlineStr"/>
     </row>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="G311" s="2" t="inlineStr"/>
     </row>
@@ -10142,7 +10142,7 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G312" s="2" t="inlineStr"/>
     </row>
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G313" s="2" t="inlineStr"/>
     </row>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="G314" s="2" t="inlineStr"/>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="G315" s="2" t="inlineStr"/>
     </row>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="G316" s="2" t="inlineStr"/>
     </row>
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="G317" s="2" t="inlineStr"/>
     </row>
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G318" s="2" t="inlineStr"/>
     </row>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="G319" s="2" t="inlineStr"/>
     </row>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G320" s="2" t="inlineStr"/>
     </row>
@@ -10421,7 +10421,7 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G321" s="2" t="inlineStr"/>
     </row>
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="G323" s="2" t="inlineStr"/>
     </row>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G324" s="2" t="inlineStr"/>
     </row>
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G326" s="2" t="inlineStr"/>
     </row>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G327" s="2" t="inlineStr"/>
     </row>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G328" s="2" t="inlineStr"/>
     </row>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G329" s="2" t="inlineStr"/>
     </row>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G330" s="2" t="inlineStr"/>
     </row>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="F331" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G331" s="2" t="inlineStr"/>
     </row>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G332" s="2" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="G333" s="2" t="inlineStr"/>
     </row>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="G334" s="2" t="inlineStr"/>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="G335" s="2" t="inlineStr"/>
     </row>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G336" s="2" t="inlineStr"/>
     </row>
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G337" s="2" t="inlineStr"/>
     </row>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G338" s="2" t="inlineStr"/>
     </row>
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G339" s="2" t="inlineStr"/>
     </row>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="F340" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G340" s="2" t="inlineStr"/>
     </row>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G341" s="2" t="inlineStr"/>
     </row>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="F342" s="2" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G342" s="2" t="inlineStr"/>
     </row>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G343" s="2" t="inlineStr"/>
     </row>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G344" s="2" t="inlineStr"/>
     </row>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G345" s="2" t="inlineStr"/>
     </row>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="F346" s="2" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="G346" s="2" t="inlineStr"/>
     </row>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="F347" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G347" s="2" t="inlineStr"/>
     </row>
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="F348" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G348" s="2" t="inlineStr"/>
     </row>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G349" s="2" t="inlineStr"/>
     </row>
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="F350" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G350" s="2" t="inlineStr"/>
     </row>
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G351" s="2" t="inlineStr"/>
     </row>
@@ -11382,7 +11382,7 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="G352" s="2" t="inlineStr"/>
     </row>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="F353" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G353" s="2" t="inlineStr"/>
     </row>
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="F354" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G354" s="2" t="inlineStr"/>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="F355" s="2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G355" s="2" t="inlineStr"/>
     </row>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="F356" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G356" s="2" t="inlineStr"/>
     </row>
@@ -11537,7 +11537,7 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G357" s="2" t="inlineStr"/>
     </row>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="F358" s="2" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="G358" s="2" t="inlineStr"/>
     </row>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="F359" s="2" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="G359" s="2" t="inlineStr"/>
     </row>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="F360" s="2" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G360" s="2" t="inlineStr"/>
     </row>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="F361" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G361" s="2" t="inlineStr"/>
     </row>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="F362" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G362" s="2" t="inlineStr"/>
     </row>
@@ -11723,7 +11723,7 @@
         </is>
       </c>
       <c r="F363" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G363" s="2" t="inlineStr"/>
     </row>
@@ -11754,7 +11754,7 @@
         </is>
       </c>
       <c r="F364" s="2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="G364" s="2" t="inlineStr"/>
     </row>
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="F365" s="2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="G365" s="2" t="inlineStr"/>
     </row>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="F367" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G367" s="2" t="inlineStr"/>
     </row>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="F368" s="2" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G368" s="2" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="F369" s="2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="G369" s="2" t="inlineStr"/>
     </row>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="F370" s="2" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G370" s="2" t="inlineStr"/>
     </row>
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="F372" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G372" s="2" t="inlineStr"/>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F373" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G373" s="2" t="inlineStr"/>
     </row>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="F374" s="2" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="G374" s="2" t="inlineStr"/>
     </row>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="F375" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G375" s="2" t="inlineStr"/>
     </row>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="F376" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G376" s="2" t="inlineStr"/>
     </row>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="F377" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G377" s="2" t="inlineStr"/>
     </row>
@@ -12188,7 +12188,7 @@
         </is>
       </c>
       <c r="F378" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="G378" s="2" t="inlineStr"/>
     </row>
@@ -12219,7 +12219,7 @@
         </is>
       </c>
       <c r="F379" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="G379" s="2" t="inlineStr"/>
     </row>
@@ -12250,7 +12250,7 @@
         </is>
       </c>
       <c r="F380" s="2" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G380" s="2" t="inlineStr"/>
     </row>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="F381" s="2" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="G381" s="2" t="inlineStr"/>
     </row>
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="F382" s="2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="G382" s="2" t="inlineStr"/>
     </row>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="F383" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G383" s="2" t="inlineStr"/>
     </row>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="F384" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G384" s="2" t="inlineStr"/>
     </row>
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="F385" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="G385" s="2" t="inlineStr"/>
     </row>
@@ -12436,7 +12436,7 @@
         </is>
       </c>
       <c r="F386" s="2" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="G386" s="2" t="inlineStr"/>
     </row>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="F387" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G387" s="2" t="inlineStr"/>
     </row>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="F388" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G388" s="2" t="inlineStr"/>
     </row>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="F389" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G389" s="2" t="inlineStr"/>
     </row>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="F390" s="2" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
     </row>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F391" s="2" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G391" s="2" t="inlineStr"/>
     </row>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="G392" s="2" t="inlineStr"/>
     </row>
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="F393" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G393" s="2" t="inlineStr"/>
     </row>
@@ -12684,7 +12684,7 @@
         </is>
       </c>
       <c r="F394" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="G394" s="2" t="inlineStr"/>
     </row>
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="F395" s="2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
     </row>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
       <c r="F396" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
     </row>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="F397" s="2" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G397" s="2" t="inlineStr"/>
     </row>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="F398" s="2" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="G398" s="2" t="inlineStr"/>
     </row>
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="F400" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G400" s="2" t="inlineStr"/>
     </row>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="F401" s="2" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="G401" s="2" t="inlineStr"/>
     </row>
@@ -12932,7 +12932,7 @@
         </is>
       </c>
       <c r="F402" s="2" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G402" s="2" t="inlineStr"/>
     </row>
@@ -12963,7 +12963,7 @@
         </is>
       </c>
       <c r="F403" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G403" s="2" t="inlineStr"/>
     </row>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="F404" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="F405" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G405" s="2" t="inlineStr"/>
     </row>
@@ -13056,7 +13056,7 @@
         </is>
       </c>
       <c r="F406" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G406" s="2" t="inlineStr"/>
     </row>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="F407" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G407" s="2" t="inlineStr"/>
     </row>
@@ -13149,7 +13149,7 @@
         </is>
       </c>
       <c r="F409" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G409" s="2" t="inlineStr"/>
     </row>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="F410" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="G410" s="2" t="inlineStr"/>
     </row>
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="F411" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G411" s="2" t="inlineStr"/>
     </row>
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="F412" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G412" s="2" t="inlineStr"/>
     </row>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="F413" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G413" s="2" t="inlineStr"/>
     </row>
@@ -13304,7 +13304,7 @@
         </is>
       </c>
       <c r="F414" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G414" s="2" t="inlineStr"/>
     </row>
@@ -13335,7 +13335,7 @@
         </is>
       </c>
       <c r="F415" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G415" s="2" t="inlineStr"/>
     </row>
@@ -13366,7 +13366,7 @@
         </is>
       </c>
       <c r="F416" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G416" s="2" t="inlineStr"/>
     </row>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="F417" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G417" s="2" t="inlineStr"/>
     </row>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="F418" s="2" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="G418" s="2" t="inlineStr"/>
     </row>
@@ -13459,7 +13459,7 @@
         </is>
       </c>
       <c r="F419" s="2" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="G419" s="2" t="inlineStr"/>
     </row>
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="F420" s="2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="G420" s="2" t="inlineStr"/>
     </row>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="F421" s="2" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="G421" s="2" t="inlineStr"/>
     </row>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="F422" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G422" s="2" t="inlineStr"/>
     </row>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="F423" s="2" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="G423" s="2" t="inlineStr"/>
     </row>
@@ -13614,7 +13614,7 @@
         </is>
       </c>
       <c r="F424" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G424" s="2" t="inlineStr"/>
     </row>
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="F426" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
     </row>
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="F427" s="2" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G427" s="2" t="inlineStr"/>
     </row>
@@ -13738,7 +13738,7 @@
         </is>
       </c>
       <c r="F428" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G428" s="2" t="inlineStr"/>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="F429" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G429" s="2" t="inlineStr"/>
     </row>
@@ -13800,7 +13800,7 @@
         </is>
       </c>
       <c r="F430" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G430" s="2" t="inlineStr"/>
     </row>
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="F431" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G431" s="2" t="inlineStr"/>
     </row>
@@ -13862,7 +13862,7 @@
         </is>
       </c>
       <c r="F432" s="2" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="G432" s="2" t="inlineStr"/>
     </row>
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="F433" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G433" s="2" t="inlineStr"/>
     </row>
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="F434" s="2" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G434" s="2" t="inlineStr"/>
     </row>
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="F435" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G435" s="2" t="inlineStr"/>
     </row>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="F436" s="2" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G436" s="2" t="inlineStr"/>
     </row>
@@ -14017,7 +14017,7 @@
         </is>
       </c>
       <c r="F437" s="2" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="G437" s="2" t="inlineStr"/>
     </row>
@@ -14048,7 +14048,7 @@
         </is>
       </c>
       <c r="F438" s="2" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="G438" s="2" t="inlineStr"/>
     </row>
@@ -14079,7 +14079,7 @@
         </is>
       </c>
       <c r="F439" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G439" s="2" t="inlineStr"/>
     </row>
@@ -14110,7 +14110,7 @@
         </is>
       </c>
       <c r="F440" s="2" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="F441" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G441" s="2" t="inlineStr"/>
     </row>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="F442" s="2" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="G442" s="2" t="inlineStr"/>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="F443" s="2" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="G443" s="2" t="inlineStr"/>
     </row>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="F444" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G444" s="2" t="inlineStr"/>
     </row>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="F446" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G446" s="2" t="inlineStr"/>
     </row>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="F447" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G447" s="2" t="inlineStr"/>
     </row>
@@ -14358,7 +14358,7 @@
         </is>
       </c>
       <c r="F448" s="2" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="G448" s="2" t="inlineStr"/>
     </row>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="F449" s="2" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G449" s="2" t="inlineStr"/>
     </row>
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="F451" s="2" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="G451" s="2" t="inlineStr"/>
     </row>
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="F452" s="2" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G452" s="2" t="inlineStr"/>
     </row>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="F453" s="2" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="G453" s="2" t="inlineStr"/>
     </row>
@@ -14544,7 +14544,7 @@
         </is>
       </c>
       <c r="F454" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G454" s="2" t="inlineStr"/>
     </row>
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="F455" s="2" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G455" s="2" t="inlineStr"/>
     </row>
@@ -14606,7 +14606,7 @@
         </is>
       </c>
       <c r="F456" s="2" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G456" s="2" t="inlineStr"/>
     </row>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="F457" s="2" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="G457" s="2" t="inlineStr"/>
     </row>
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="F458" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G458" s="2" t="inlineStr"/>
     </row>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="F459" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G459" s="2" t="inlineStr"/>
     </row>
@@ -14730,7 +14730,7 @@
         </is>
       </c>
       <c r="F460" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G460" s="2" t="inlineStr"/>
     </row>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="F461" s="2" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G461" s="2" t="inlineStr"/>
     </row>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="F462" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G462" s="2" t="inlineStr"/>
     </row>
@@ -14823,7 +14823,7 @@
         </is>
       </c>
       <c r="F463" s="2" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G463" s="2" t="inlineStr"/>
     </row>
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="F464" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G464" s="2" t="inlineStr"/>
     </row>
@@ -14885,7 +14885,7 @@
         </is>
       </c>
       <c r="F465" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G465" s="2" t="inlineStr"/>
     </row>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="F466" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G466" s="2" t="inlineStr"/>
     </row>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="F468" s="2" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="G468" s="2" t="inlineStr"/>
     </row>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="F469" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G469" s="2" t="inlineStr"/>
     </row>
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="F470" s="2" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="G470" s="2" t="inlineStr"/>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="F471" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G471" s="2" t="inlineStr"/>
     </row>
@@ -15162,7 +15162,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
     </row>
@@ -15255,7 +15255,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -15379,7 +15379,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
@@ -15472,7 +15472,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
@@ -15596,7 +15596,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
     </row>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
     </row>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -15751,7 +15751,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -15844,7 +15844,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -15875,7 +15875,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
@@ -15906,7 +15906,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -15999,7 +15999,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
     </row>
@@ -16030,7 +16030,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
     </row>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -16123,7 +16123,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
@@ -16216,7 +16216,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -16247,7 +16247,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
     </row>
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
     </row>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>
@@ -16371,7 +16371,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
     </row>
@@ -16402,7 +16402,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
     </row>
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
     </row>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
     </row>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
     </row>
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
     </row>
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
     </row>
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
     </row>
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
     </row>
@@ -16650,7 +16650,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
     </row>
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
     </row>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
     </row>
@@ -16743,7 +16743,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
     </row>
@@ -16774,7 +16774,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
     </row>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
     </row>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
     </row>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
     </row>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
     </row>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
     </row>
@@ -16991,7 +16991,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
     </row>
@@ -17022,7 +17022,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
@@ -17084,7 +17084,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
     </row>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
     </row>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
     </row>
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
     </row>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
     </row>
@@ -17239,7 +17239,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
     </row>
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
     </row>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
     </row>
@@ -17332,7 +17332,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
     </row>
@@ -17394,7 +17394,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
     </row>
@@ -17425,7 +17425,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
     </row>
@@ -17456,7 +17456,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
     </row>
@@ -17487,7 +17487,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
     </row>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
     </row>
@@ -17549,7 +17549,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
     </row>
@@ -17580,7 +17580,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
     </row>
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
     </row>
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
     </row>
@@ -17673,7 +17673,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
     </row>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
     </row>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
     </row>
@@ -17766,7 +17766,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
     </row>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
     </row>
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
     </row>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
     </row>
@@ -17890,7 +17890,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
     </row>
@@ -17952,7 +17952,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
     </row>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
     </row>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
     </row>
@@ -18045,7 +18045,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
     </row>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
     </row>
@@ -18107,7 +18107,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
     </row>
@@ -18138,7 +18138,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
     </row>
@@ -18169,7 +18169,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
     </row>
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
     </row>
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
     </row>
@@ -18262,7 +18262,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
     </row>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
     </row>
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
     </row>
@@ -18355,7 +18355,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
     </row>
@@ -18386,7 +18386,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
     </row>
@@ -18417,7 +18417,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
     </row>
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
     </row>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
     </row>
@@ -18510,7 +18510,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
     </row>
@@ -18541,7 +18541,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
     </row>
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
     </row>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
     </row>
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
     </row>
@@ -18696,7 +18696,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
     </row>
@@ -18727,7 +18727,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
     </row>
@@ -18758,7 +18758,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
     </row>
@@ -18789,7 +18789,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
     </row>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
     </row>
@@ -18851,7 +18851,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
     </row>
@@ -18882,7 +18882,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
     </row>
@@ -18913,7 +18913,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
     </row>
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
     </row>
@@ -18975,7 +18975,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
     </row>
@@ -19006,7 +19006,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
     </row>
@@ -19068,7 +19068,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
     </row>
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
     </row>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
     </row>
@@ -19161,7 +19161,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
     </row>
@@ -19192,7 +19192,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
     </row>
@@ -19223,7 +19223,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
     </row>
@@ -19254,7 +19254,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
     </row>
@@ -19285,7 +19285,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
     </row>
@@ -19316,7 +19316,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
     </row>
@@ -19347,7 +19347,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
     </row>
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
     </row>
@@ -19409,7 +19409,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
     </row>
@@ -19440,7 +19440,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
     </row>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
     </row>
@@ -19502,7 +19502,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
     </row>
@@ -19533,7 +19533,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
     </row>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
     </row>
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
     </row>
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
     </row>
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
     </row>
@@ -19688,7 +19688,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
     </row>
@@ -19719,7 +19719,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
     </row>
@@ -19750,7 +19750,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
     </row>
@@ -19781,7 +19781,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
     </row>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
     </row>
@@ -19874,7 +19874,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
     </row>
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="G155" s="2" t="inlineStr"/>
     </row>
@@ -19936,7 +19936,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
     </row>
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
     </row>
@@ -19998,7 +19998,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
     </row>
@@ -20029,7 +20029,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
     </row>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
     </row>
@@ -20091,7 +20091,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
     </row>
@@ -20122,7 +20122,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
     </row>
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
     </row>
@@ -20246,7 +20246,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
     </row>
@@ -20277,7 +20277,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
     </row>
@@ -20308,7 +20308,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
     </row>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
     </row>
@@ -20370,7 +20370,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
     </row>
@@ -20401,7 +20401,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
     </row>
@@ -20432,7 +20432,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
     </row>
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
     </row>
@@ -20494,7 +20494,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
     </row>
@@ -20525,7 +20525,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
     </row>
@@ -20556,7 +20556,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
     </row>
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G177" s="2" t="inlineStr"/>
     </row>
@@ -20618,7 +20618,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
     </row>
@@ -20649,7 +20649,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
     </row>
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
     </row>
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
     </row>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
     </row>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
     </row>
@@ -20804,7 +20804,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
     </row>
@@ -20835,7 +20835,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
     </row>
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
     </row>
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G187" s="2" t="inlineStr"/>
     </row>
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
     </row>
@@ -20959,7 +20959,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
     </row>
@@ -20990,7 +20990,7 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
     </row>
@@ -21021,7 +21021,7 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
     </row>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
     </row>
@@ -21083,7 +21083,7 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="G193" s="2" t="inlineStr"/>
     </row>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G194" s="2" t="inlineStr"/>
     </row>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="G195" s="2" t="inlineStr"/>
     </row>
@@ -21176,7 +21176,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
     </row>
@@ -21207,7 +21207,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="G197" s="2" t="inlineStr"/>
     </row>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="G198" s="2" t="inlineStr"/>
     </row>
@@ -21269,7 +21269,7 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G199" s="2" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="G200" s="2" t="inlineStr"/>
     </row>
@@ -21331,7 +21331,7 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="G201" s="2" t="inlineStr"/>
     </row>
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
     </row>
@@ -21393,7 +21393,7 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G203" s="2" t="inlineStr"/>
     </row>
@@ -21424,7 +21424,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G204" s="2" t="inlineStr"/>
     </row>
@@ -21455,7 +21455,7 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="G205" s="2" t="inlineStr"/>
     </row>
@@ -21486,7 +21486,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G206" s="2" t="inlineStr"/>
     </row>
@@ -21517,7 +21517,7 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="G207" s="2" t="inlineStr"/>
     </row>
@@ -21548,7 +21548,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G208" s="2" t="inlineStr"/>
     </row>
@@ -21610,7 +21610,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="G210" s="2" t="inlineStr"/>
     </row>
@@ -21672,7 +21672,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G212" s="2" t="inlineStr"/>
     </row>
@@ -21703,7 +21703,7 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G213" s="2" t="inlineStr"/>
     </row>
@@ -21734,7 +21734,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="G214" s="2" t="inlineStr"/>
     </row>
@@ -21765,7 +21765,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G215" s="2" t="inlineStr"/>
     </row>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="G217" s="2" t="inlineStr"/>
     </row>
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G218" s="2" t="inlineStr"/>
     </row>
@@ -21889,7 +21889,7 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
     </row>
@@ -21920,7 +21920,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
     </row>
@@ -21951,7 +21951,7 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G221" s="2" t="inlineStr"/>
     </row>
@@ -21982,7 +21982,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G222" s="2" t="inlineStr"/>
     </row>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G223" s="2" t="inlineStr"/>
     </row>
@@ -22044,7 +22044,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="G224" s="2" t="inlineStr"/>
     </row>
@@ -22075,7 +22075,7 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G225" s="2" t="inlineStr"/>
     </row>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="G226" s="2" t="inlineStr"/>
     </row>
@@ -22137,7 +22137,7 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G227" s="2" t="inlineStr"/>
     </row>
@@ -22168,7 +22168,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G228" s="2" t="inlineStr"/>
     </row>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="G229" s="2" t="inlineStr"/>
     </row>
@@ -22230,7 +22230,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G230" s="2" t="inlineStr"/>
     </row>
@@ -22261,7 +22261,7 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G231" s="2" t="inlineStr"/>
     </row>
@@ -22292,7 +22292,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G232" s="2" t="inlineStr"/>
     </row>
@@ -22323,7 +22323,7 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G233" s="2" t="inlineStr"/>
     </row>
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="G234" s="2" t="inlineStr"/>
     </row>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G235" s="2" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G236" s="2" t="inlineStr"/>
     </row>
@@ -22447,7 +22447,7 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G237" s="2" t="inlineStr"/>
     </row>
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G238" s="2" t="inlineStr"/>
     </row>
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G239" s="2" t="inlineStr"/>
     </row>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="G241" s="2" t="inlineStr"/>
     </row>
@@ -22602,7 +22602,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="G242" s="2" t="inlineStr"/>
     </row>
@@ -22664,7 +22664,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G244" s="2" t="inlineStr"/>
     </row>
@@ -22695,7 +22695,7 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G245" s="2" t="inlineStr"/>
     </row>
@@ -22726,7 +22726,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G246" s="2" t="inlineStr"/>
     </row>
@@ -22757,7 +22757,7 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="G247" s="2" t="inlineStr"/>
     </row>
@@ -22788,7 +22788,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G248" s="2" t="inlineStr"/>
     </row>
@@ -22819,7 +22819,7 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G249" s="2" t="inlineStr"/>
     </row>
@@ -22850,7 +22850,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G250" s="2" t="inlineStr"/>
     </row>
@@ -22881,7 +22881,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G251" s="2" t="inlineStr"/>
     </row>
@@ -22943,7 +22943,7 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="G253" s="2" t="inlineStr"/>
     </row>
@@ -22974,7 +22974,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="G254" s="2" t="inlineStr"/>
     </row>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="G256" s="2" t="inlineStr"/>
     </row>
@@ -23067,7 +23067,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G257" s="2" t="inlineStr"/>
     </row>
@@ -23098,7 +23098,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G258" s="2" t="inlineStr"/>
     </row>
@@ -23129,7 +23129,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G259" s="2" t="inlineStr"/>
     </row>
@@ -23160,7 +23160,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G260" s="2" t="inlineStr"/>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G261" s="2" t="inlineStr"/>
     </row>
@@ -23222,7 +23222,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G262" s="2" t="inlineStr"/>
     </row>
@@ -23253,7 +23253,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="G263" s="2" t="inlineStr"/>
     </row>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G264" s="2" t="inlineStr"/>
     </row>
@@ -23315,7 +23315,7 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G265" s="2" t="inlineStr"/>
     </row>
@@ -23346,7 +23346,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="G266" s="2" t="inlineStr"/>
     </row>
@@ -23408,7 +23408,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G268" s="2" t="inlineStr"/>
     </row>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G269" s="2" t="inlineStr"/>
     </row>
@@ -23470,7 +23470,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G270" s="2" t="inlineStr"/>
     </row>
@@ -23501,7 +23501,7 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="G271" s="2" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G272" s="2" t="inlineStr"/>
     </row>
@@ -23563,7 +23563,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="G273" s="2" t="inlineStr"/>
     </row>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="G274" s="2" t="inlineStr"/>
     </row>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G275" s="2" t="inlineStr"/>
     </row>
@@ -23656,7 +23656,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="G276" s="2" t="inlineStr"/>
     </row>
@@ -23687,7 +23687,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G277" s="2" t="inlineStr"/>
     </row>
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="G279" s="2" t="inlineStr"/>
     </row>
@@ -23780,7 +23780,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G280" s="2" t="inlineStr"/>
     </row>
@@ -23811,7 +23811,7 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="G281" s="2" t="inlineStr"/>
     </row>
@@ -23842,7 +23842,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G282" s="2" t="inlineStr"/>
     </row>
@@ -23904,7 +23904,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G284" s="2" t="inlineStr"/>
     </row>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="G285" s="2" t="inlineStr"/>
     </row>
@@ -23966,7 +23966,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="G286" s="2" t="inlineStr"/>
     </row>
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G287" s="2" t="inlineStr"/>
     </row>
@@ -24028,7 +24028,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="G288" s="2" t="inlineStr"/>
     </row>
@@ -24059,7 +24059,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G289" s="2" t="inlineStr"/>
     </row>
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G290" s="2" t="inlineStr"/>
     </row>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="G291" s="2" t="inlineStr"/>
     </row>
@@ -24152,7 +24152,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G292" s="2" t="inlineStr"/>
     </row>
@@ -24183,7 +24183,7 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G293" s="2" t="inlineStr"/>
     </row>
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G294" s="2" t="inlineStr"/>
     </row>
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="G295" s="2" t="inlineStr"/>
     </row>
@@ -24276,7 +24276,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="G296" s="2" t="inlineStr"/>
     </row>
@@ -24307,7 +24307,7 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G297" s="2" t="inlineStr"/>
     </row>
@@ -24338,7 +24338,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="G298" s="2" t="inlineStr"/>
     </row>
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G299" s="2" t="inlineStr"/>
     </row>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="G300" s="2" t="inlineStr"/>
     </row>
@@ -24431,7 +24431,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G301" s="2" t="inlineStr"/>
     </row>
@@ -24462,7 +24462,7 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="G302" s="2" t="inlineStr"/>
     </row>
@@ -24493,7 +24493,7 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G303" s="2" t="inlineStr"/>
     </row>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G304" s="2" t="inlineStr"/>
     </row>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="G305" s="2" t="inlineStr"/>
     </row>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G306" s="2" t="inlineStr"/>
     </row>
@@ -24617,7 +24617,7 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="G307" s="2" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="G308" s="2" t="inlineStr"/>
     </row>
@@ -24679,7 +24679,7 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G309" s="2" t="inlineStr"/>
     </row>
@@ -24710,7 +24710,7 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="G310" s="2" t="inlineStr"/>
     </row>
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="G311" s="2" t="inlineStr"/>
     </row>
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G312" s="2" t="inlineStr"/>
     </row>
@@ -24803,7 +24803,7 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G313" s="2" t="inlineStr"/>
     </row>
@@ -24834,7 +24834,7 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="G314" s="2" t="inlineStr"/>
     </row>
@@ -24865,7 +24865,7 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="G315" s="2" t="inlineStr"/>
     </row>
@@ -24896,7 +24896,7 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="G316" s="2" t="inlineStr"/>
     </row>
@@ -24927,7 +24927,7 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="G317" s="2" t="inlineStr"/>
     </row>
@@ -24958,7 +24958,7 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G318" s="2" t="inlineStr"/>
     </row>
@@ -24989,7 +24989,7 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="G319" s="2" t="inlineStr"/>
     </row>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G320" s="2" t="inlineStr"/>
     </row>
@@ -25051,7 +25051,7 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G321" s="2" t="inlineStr"/>
     </row>
@@ -25113,7 +25113,7 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="G323" s="2" t="inlineStr"/>
     </row>
@@ -25144,7 +25144,7 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="G324" s="2" t="inlineStr"/>
     </row>
@@ -25206,7 +25206,7 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G326" s="2" t="inlineStr"/>
     </row>
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G327" s="2" t="inlineStr"/>
     </row>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G328" s="2" t="inlineStr"/>
     </row>
@@ -25299,7 +25299,7 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G329" s="2" t="inlineStr"/>
     </row>
@@ -25330,7 +25330,7 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G330" s="2" t="inlineStr"/>
     </row>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="F331" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G331" s="2" t="inlineStr"/>
     </row>
@@ -25392,7 +25392,7 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G332" s="2" t="inlineStr"/>
     </row>
@@ -25423,7 +25423,7 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="G333" s="2" t="inlineStr"/>
     </row>
@@ -25454,7 +25454,7 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="G334" s="2" t="inlineStr"/>
     </row>
@@ -25485,7 +25485,7 @@
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="G335" s="2" t="inlineStr"/>
     </row>
@@ -25516,7 +25516,7 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G336" s="2" t="inlineStr"/>
     </row>
@@ -25547,7 +25547,7 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G337" s="2" t="inlineStr"/>
     </row>
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G338" s="2" t="inlineStr"/>
     </row>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G339" s="2" t="inlineStr"/>
     </row>
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="F340" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G340" s="2" t="inlineStr"/>
     </row>
@@ -25671,7 +25671,7 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G341" s="2" t="inlineStr"/>
     </row>
@@ -25702,7 +25702,7 @@
         </is>
       </c>
       <c r="F342" s="2" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G342" s="2" t="inlineStr"/>
     </row>
@@ -25733,7 +25733,7 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G343" s="2" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G344" s="2" t="inlineStr"/>
     </row>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="G345" s="2" t="inlineStr"/>
     </row>
@@ -25826,7 +25826,7 @@
         </is>
       </c>
       <c r="F346" s="2" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="G346" s="2" t="inlineStr"/>
     </row>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="F347" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G347" s="2" t="inlineStr"/>
     </row>
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="F348" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G348" s="2" t="inlineStr"/>
     </row>
@@ -25919,7 +25919,7 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G349" s="2" t="inlineStr"/>
     </row>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="F350" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G350" s="2" t="inlineStr"/>
     </row>
@@ -25981,7 +25981,7 @@
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G351" s="2" t="inlineStr"/>
     </row>
@@ -26012,7 +26012,7 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="G352" s="2" t="inlineStr"/>
     </row>
@@ -26043,7 +26043,7 @@
         </is>
       </c>
       <c r="F353" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G353" s="2" t="inlineStr"/>
     </row>
@@ -26074,7 +26074,7 @@
         </is>
       </c>
       <c r="F354" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G354" s="2" t="inlineStr"/>
     </row>
@@ -26105,7 +26105,7 @@
         </is>
       </c>
       <c r="F355" s="2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G355" s="2" t="inlineStr"/>
     </row>
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="F356" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G356" s="2" t="inlineStr"/>
     </row>
@@ -26167,7 +26167,7 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G357" s="2" t="inlineStr"/>
     </row>
@@ -26198,7 +26198,7 @@
         </is>
       </c>
       <c r="F358" s="2" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="G358" s="2" t="inlineStr"/>
     </row>
@@ -26229,7 +26229,7 @@
         </is>
       </c>
       <c r="F359" s="2" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="G359" s="2" t="inlineStr"/>
     </row>
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="F360" s="2" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G360" s="2" t="inlineStr"/>
     </row>
@@ -26291,7 +26291,7 @@
         </is>
       </c>
       <c r="F361" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="G361" s="2" t="inlineStr"/>
     </row>
@@ -26322,7 +26322,7 @@
         </is>
       </c>
       <c r="F362" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G362" s="2" t="inlineStr"/>
     </row>
@@ -26353,7 +26353,7 @@
         </is>
       </c>
       <c r="F363" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G363" s="2" t="inlineStr"/>
     </row>
@@ -26384,7 +26384,7 @@
         </is>
       </c>
       <c r="F364" s="2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="G364" s="2" t="inlineStr"/>
     </row>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="F365" s="2" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="G365" s="2" t="inlineStr"/>
     </row>
@@ -26477,7 +26477,7 @@
         </is>
       </c>
       <c r="F367" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G367" s="2" t="inlineStr"/>
     </row>
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="F368" s="2" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G368" s="2" t="inlineStr"/>
     </row>
@@ -26539,7 +26539,7 @@
         </is>
       </c>
       <c r="F369" s="2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="G369" s="2" t="inlineStr"/>
     </row>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="F370" s="2" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G370" s="2" t="inlineStr"/>
     </row>
@@ -26632,7 +26632,7 @@
         </is>
       </c>
       <c r="F372" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G372" s="2" t="inlineStr"/>
     </row>
@@ -26663,7 +26663,7 @@
         </is>
       </c>
       <c r="F373" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G373" s="2" t="inlineStr"/>
     </row>
@@ -26694,7 +26694,7 @@
         </is>
       </c>
       <c r="F374" s="2" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="G374" s="2" t="inlineStr"/>
     </row>
@@ -26725,7 +26725,7 @@
         </is>
       </c>
       <c r="F375" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G375" s="2" t="inlineStr"/>
     </row>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="F376" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G376" s="2" t="inlineStr"/>
     </row>
@@ -26787,7 +26787,7 @@
         </is>
       </c>
       <c r="F377" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="G377" s="2" t="inlineStr"/>
     </row>
@@ -26818,7 +26818,7 @@
         </is>
       </c>
       <c r="F378" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="G378" s="2" t="inlineStr"/>
     </row>
@@ -26849,7 +26849,7 @@
         </is>
       </c>
       <c r="F379" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="G379" s="2" t="inlineStr"/>
     </row>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="F380" s="2" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="G380" s="2" t="inlineStr"/>
     </row>
@@ -26911,7 +26911,7 @@
         </is>
       </c>
       <c r="F381" s="2" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="G381" s="2" t="inlineStr"/>
     </row>
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="F382" s="2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="G382" s="2" t="inlineStr"/>
     </row>
@@ -26973,7 +26973,7 @@
         </is>
       </c>
       <c r="F383" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G383" s="2" t="inlineStr"/>
     </row>
@@ -27004,7 +27004,7 @@
         </is>
       </c>
       <c r="F384" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G384" s="2" t="inlineStr"/>
     </row>
@@ -27035,7 +27035,7 @@
         </is>
       </c>
       <c r="F385" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="G385" s="2" t="inlineStr"/>
     </row>
@@ -27066,7 +27066,7 @@
         </is>
       </c>
       <c r="F386" s="2" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="G386" s="2" t="inlineStr"/>
     </row>
@@ -27097,7 +27097,7 @@
         </is>
       </c>
       <c r="F387" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G387" s="2" t="inlineStr"/>
     </row>
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="F388" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G388" s="2" t="inlineStr"/>
     </row>
@@ -27159,7 +27159,7 @@
         </is>
       </c>
       <c r="F389" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G389" s="2" t="inlineStr"/>
     </row>
@@ -27190,7 +27190,7 @@
         </is>
       </c>
       <c r="F390" s="2" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
     </row>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="F391" s="2" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G391" s="2" t="inlineStr"/>
     </row>
@@ -27252,7 +27252,7 @@
         </is>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="G392" s="2" t="inlineStr"/>
     </row>
@@ -27283,7 +27283,7 @@
         </is>
       </c>
       <c r="F393" s="2" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="G393" s="2" t="inlineStr"/>
     </row>
@@ -27314,7 +27314,7 @@
         </is>
       </c>
       <c r="F394" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="G394" s="2" t="inlineStr"/>
     </row>
@@ -27345,7 +27345,7 @@
         </is>
       </c>
       <c r="F395" s="2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
     </row>
@@ -27376,7 +27376,7 @@
         </is>
       </c>
       <c r="F396" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
     </row>
@@ -27407,7 +27407,7 @@
         </is>
       </c>
       <c r="F397" s="2" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G397" s="2" t="inlineStr"/>
     </row>
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="F398" s="2" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="G398" s="2" t="inlineStr"/>
     </row>
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="F400" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G400" s="2" t="inlineStr"/>
     </row>
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="F401" s="2" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="G401" s="2" t="inlineStr"/>
     </row>
@@ -27562,7 +27562,7 @@
         </is>
       </c>
       <c r="F402" s="2" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G402" s="2" t="inlineStr"/>
     </row>
@@ -27593,7 +27593,7 @@
         </is>
       </c>
       <c r="F403" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G403" s="2" t="inlineStr"/>
     </row>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="F404" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
     </row>
@@ -27655,7 +27655,7 @@
         </is>
       </c>
       <c r="F405" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G405" s="2" t="inlineStr"/>
     </row>
@@ -27686,7 +27686,7 @@
         </is>
       </c>
       <c r="F406" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G406" s="2" t="inlineStr"/>
     </row>
@@ -27717,7 +27717,7 @@
         </is>
       </c>
       <c r="F407" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G407" s="2" t="inlineStr"/>
     </row>
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="F409" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G409" s="2" t="inlineStr"/>
     </row>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="F410" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="G410" s="2" t="inlineStr"/>
     </row>
@@ -27841,7 +27841,7 @@
         </is>
       </c>
       <c r="F411" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G411" s="2" t="inlineStr"/>
     </row>
@@ -27872,7 +27872,7 @@
         </is>
       </c>
       <c r="F412" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G412" s="2" t="inlineStr"/>
     </row>
@@ -27903,7 +27903,7 @@
         </is>
       </c>
       <c r="F413" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G413" s="2" t="inlineStr"/>
     </row>
@@ -27934,7 +27934,7 @@
         </is>
       </c>
       <c r="F414" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G414" s="2" t="inlineStr"/>
     </row>
@@ -27965,7 +27965,7 @@
         </is>
       </c>
       <c r="F415" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G415" s="2" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="F416" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="G416" s="2" t="inlineStr"/>
     </row>
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="F417" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G417" s="2" t="inlineStr"/>
     </row>
@@ -28058,7 +28058,7 @@
         </is>
       </c>
       <c r="F418" s="2" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="G418" s="2" t="inlineStr"/>
     </row>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="F419" s="2" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="G419" s="2" t="inlineStr"/>
     </row>
@@ -28120,7 +28120,7 @@
         </is>
       </c>
       <c r="F420" s="2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="G420" s="2" t="inlineStr"/>
     </row>
@@ -28151,7 +28151,7 @@
         </is>
       </c>
       <c r="F421" s="2" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="G421" s="2" t="inlineStr"/>
     </row>
@@ -28182,7 +28182,7 @@
         </is>
       </c>
       <c r="F422" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G422" s="2" t="inlineStr"/>
     </row>
@@ -28213,7 +28213,7 @@
         </is>
       </c>
       <c r="F423" s="2" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="G423" s="2" t="inlineStr"/>
     </row>
@@ -28244,7 +28244,7 @@
         </is>
       </c>
       <c r="F424" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G424" s="2" t="inlineStr"/>
     </row>
@@ -28306,7 +28306,7 @@
         </is>
       </c>
       <c r="F426" s="2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
     </row>
@@ -28337,7 +28337,7 @@
         </is>
       </c>
       <c r="F427" s="2" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G427" s="2" t="inlineStr"/>
     </row>
@@ -28368,7 +28368,7 @@
         </is>
       </c>
       <c r="F428" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G428" s="2" t="inlineStr"/>
     </row>
@@ -28399,7 +28399,7 @@
         </is>
       </c>
       <c r="F429" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G429" s="2" t="inlineStr"/>
     </row>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="F430" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G430" s="2" t="inlineStr"/>
     </row>
@@ -28461,7 +28461,7 @@
         </is>
       </c>
       <c r="F431" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G431" s="2" t="inlineStr"/>
     </row>
@@ -28492,7 +28492,7 @@
         </is>
       </c>
       <c r="F432" s="2" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="G432" s="2" t="inlineStr"/>
     </row>
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="F433" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G433" s="2" t="inlineStr"/>
     </row>
@@ -28554,7 +28554,7 @@
         </is>
       </c>
       <c r="F434" s="2" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G434" s="2" t="inlineStr"/>
     </row>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="F435" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G435" s="2" t="inlineStr"/>
     </row>
@@ -28616,7 +28616,7 @@
         </is>
       </c>
       <c r="F436" s="2" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G436" s="2" t="inlineStr"/>
     </row>
@@ -28647,7 +28647,7 @@
         </is>
       </c>
       <c r="F437" s="2" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="G437" s="2" t="inlineStr"/>
     </row>
@@ -28678,7 +28678,7 @@
         </is>
       </c>
       <c r="F438" s="2" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="G438" s="2" t="inlineStr"/>
     </row>
@@ -28709,7 +28709,7 @@
         </is>
       </c>
       <c r="F439" s="2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="G439" s="2" t="inlineStr"/>
     </row>
@@ -28740,7 +28740,7 @@
         </is>
       </c>
       <c r="F440" s="2" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
     </row>
@@ -28771,7 +28771,7 @@
         </is>
       </c>
       <c r="F441" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G441" s="2" t="inlineStr"/>
     </row>
@@ -28802,7 +28802,7 @@
         </is>
       </c>
       <c r="F442" s="2" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="G442" s="2" t="inlineStr"/>
     </row>
@@ -28833,7 +28833,7 @@
         </is>
       </c>
       <c r="F443" s="2" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="G443" s="2" t="inlineStr"/>
     </row>
@@ -28864,7 +28864,7 @@
         </is>
       </c>
       <c r="F444" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="G444" s="2" t="inlineStr"/>
     </row>
@@ -28926,7 +28926,7 @@
         </is>
       </c>
       <c r="F446" s="2" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G446" s="2" t="inlineStr"/>
     </row>
@@ -28957,7 +28957,7 @@
         </is>
       </c>
       <c r="F447" s="2" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G447" s="2" t="inlineStr"/>
     </row>
@@ -28988,7 +28988,7 @@
         </is>
       </c>
       <c r="F448" s="2" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="G448" s="2" t="inlineStr"/>
     </row>
@@ -29019,7 +29019,7 @@
         </is>
       </c>
       <c r="F449" s="2" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="G449" s="2" t="inlineStr"/>
     </row>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="F451" s="2" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="G451" s="2" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="F452" s="2" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G452" s="2" t="inlineStr"/>
     </row>
@@ -29143,7 +29143,7 @@
         </is>
       </c>
       <c r="F453" s="2" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="G453" s="2" t="inlineStr"/>
     </row>
@@ -29174,7 +29174,7 @@
         </is>
       </c>
       <c r="F454" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="G454" s="2" t="inlineStr"/>
     </row>
@@ -29205,7 +29205,7 @@
         </is>
       </c>
       <c r="F455" s="2" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G455" s="2" t="inlineStr"/>
     </row>
@@ -29236,7 +29236,7 @@
         </is>
       </c>
       <c r="F456" s="2" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G456" s="2" t="inlineStr"/>
     </row>
@@ -29267,7 +29267,7 @@
         </is>
       </c>
       <c r="F457" s="2" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="G457" s="2" t="inlineStr"/>
     </row>
@@ -29298,7 +29298,7 @@
         </is>
       </c>
       <c r="F458" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G458" s="2" t="inlineStr"/>
     </row>
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="F459" s="2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G459" s="2" t="inlineStr"/>
     </row>
@@ -29360,7 +29360,7 @@
         </is>
       </c>
       <c r="F460" s="2" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="G460" s="2" t="inlineStr"/>
     </row>
@@ -29391,7 +29391,7 @@
         </is>
       </c>
       <c r="F461" s="2" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G461" s="2" t="inlineStr"/>
     </row>
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="F462" s="2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="G462" s="2" t="inlineStr"/>
     </row>
@@ -29453,7 +29453,7 @@
         </is>
       </c>
       <c r="F463" s="2" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G463" s="2" t="inlineStr"/>
     </row>
@@ -29484,7 +29484,7 @@
         </is>
       </c>
       <c r="F464" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G464" s="2" t="inlineStr"/>
     </row>
@@ -29515,7 +29515,7 @@
         </is>
       </c>
       <c r="F465" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G465" s="2" t="inlineStr"/>
     </row>
@@ -29546,7 +29546,7 @@
         </is>
       </c>
       <c r="F466" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G466" s="2" t="inlineStr"/>
     </row>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="F468" s="2" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="G468" s="2" t="inlineStr"/>
     </row>
@@ -29639,7 +29639,7 @@
         </is>
       </c>
       <c r="F469" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G469" s="2" t="inlineStr"/>
     </row>
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="F470" s="2" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="G470" s="2" t="inlineStr"/>
     </row>
@@ -29701,7 +29701,7 @@
         </is>
       </c>
       <c r="F471" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G471" s="2" t="inlineStr"/>
     </row>
@@ -29925,7 +29925,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4.5s</t>
+          <t>6.7s</t>
         </is>
       </c>
     </row>
